--- a/source/Sylvan.Data.Excel.Tests/Data/Numbers.xlsx
+++ b/source/Sylvan.Data.Excel.Tests/Data/Numbers.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mark\source\Sylvan.Data.Excel\source\Sylvan.Data.Excel.Tests\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markp\source\Sylvan.Data.Excel\source\Sylvan.Data.Excel.Tests\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF86835-D857-49A8-B3CF-8B1C19AD2830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D181EF-5C65-4560-83AD-F71D6FA2736C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="2985" windowWidth="21600" windowHeight="12735" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2808" yWindow="3840" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -367,13 +367,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>3.3</v>
       </c>
@@ -391,6 +393,12 @@
       </c>
       <c r="F1">
         <v>-9303.83</v>
+      </c>
+      <c r="G1">
+        <v>150000000</v>
+      </c>
+      <c r="H1">
+        <v>1.4999999999999999E-7</v>
       </c>
     </row>
   </sheetData>
